--- a/planning/VitaSync_Coding_Backlog.xlsx
+++ b/planning/VitaSync_Coding_Backlog.xlsx
@@ -344,8 +344,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TasksTable" displayName="TasksTable" ref="A3:T139" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A3:T139"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TasksTable" displayName="TasksTable" ref="A3:T141" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A3:T141"/>
   <tableColumns count="20">
     <tableColumn id="1" name="Task-ID"/>
     <tableColumn id="2" name="Story-ID"/>
@@ -372,8 +372,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="BriefingsTable" displayName="BriefingsTable" ref="A3:G139" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A3:G139"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="BriefingsTable" displayName="BriefingsTable" ref="A3:G141" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A3:G141"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Task-ID"/>
     <tableColumn id="2" name="Konkreter Auftrag"/>
@@ -637,10 +637,13 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>33 User Stories (U001–U033) und 136 Tasks einschließlich 18 Grundlagen. Nach D08 (kein Medizinprodukt) sind 4 Stories mit 13 Tasks gestrichen und weitere umgebaut; nach D09 (EU-Datenschutz, AI Act) kamen F016–F018, T-U028-03 und U033 hinzu. Siehe Spalten „Zweckprüfung (D08)“ und „Änderung“.</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="n"/>
+          <t>User Stories U001–U033 und die in der Spalte Anzahl gezaehlten Tasks, einschliesslich 18 Grundlagen. Nach D08 (kein Medizinprodukt) sind 4 Stories mit 13 Tasks gestrichen und weitere umgebaut; nach D09 (EU-Datenschutz, AI Act) kamen F016–F018, T-U028-03 und U033 hinzu. Siehe Spalten „Zweckprüfung (D08)“ und „Änderung“.</t>
+        </is>
+      </c>
+      <c r="C4" s="15">
+        <f>COUNTIFS(Tasks!$A$4:$A$1000,"&lt;&gt;")</f>
+        <v/>
+      </c>
     </row>
     <row r="5" ht="67.5" customHeight="1" s="11">
       <c r="A5" s="16" t="inlineStr">
@@ -650,7 +653,7 @@
       </c>
       <c r="B5" s="16" t="n"/>
       <c r="C5" s="16">
-        <f>COUNTIFS(Tasks!$M$4:$M$139,"&lt;&gt;Erledigt",Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$M$4:$M$1000,"&lt;&gt;Erledigt",Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen",Tasks!$A$4:$A$1000,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -662,7 +665,7 @@
       </c>
       <c r="B6" s="15" t="n"/>
       <c r="C6" s="15">
-        <f>COUNTIFS(Tasks!$M$4:$M$139,"Erledigt")</f>
+        <f>COUNTIFS(Tasks!$M$4:$M$1000,"Erledigt")</f>
         <v/>
       </c>
     </row>
@@ -739,7 +742,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Ein Bearbeiter pro Task. Nach Implementierung: Im Review. Eine andere Person prüft und integriert. Erst dann Erledigt. Status und Zuweisung laufen über GitHub Issues (docs/Arbeitsablauf.md); diese Datei ist der Plan.</t>
+          <t>Ein Bearbeiter pro Task. Nach Implementierung: Im Review. Eine andere Person prüft und integriert; im Testlauf (D10) übernimmt eine Person alle Rollen und das Review ist die eigene Durchsicht des Diffs vor dem Merge. Erst dann Erledigt. Statusquelle ist die Spalte Status im Blatt Tasks; der Pull Request ist der Nachweis, in dem die Zeile im selben Zug gepflegt wird (docs/Arbeitsablauf.md). GitHub Issues sind optional.</t>
         </is>
       </c>
       <c r="C12" s="15" t="n"/>
@@ -817,7 +820,7 @@
       </c>
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="15">
-        <f>COUNTIFS(Tasks!$M$4:$M$139,"Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$M$4:$M$1000,"Gestrichen")</f>
         <v/>
       </c>
     </row>
@@ -992,7 +995,7 @@
         </is>
       </c>
       <c r="J4" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A4,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A4,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K4" s="15" t="inlineStr">
@@ -1051,7 +1054,7 @@
         </is>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A5,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A5,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K5" s="16" t="inlineStr">
@@ -1110,7 +1113,7 @@
         </is>
       </c>
       <c r="J6" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A6,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A6,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K6" s="15" t="inlineStr">
@@ -1169,7 +1172,7 @@
         </is>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A7,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A7,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K7" s="16" t="inlineStr">
@@ -1224,7 +1227,7 @@
         </is>
       </c>
       <c r="J8" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A8,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A8,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K8" s="15" t="inlineStr">
@@ -1279,7 +1282,7 @@
         </is>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A9,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A9,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K9" s="16" t="inlineStr">
@@ -1338,7 +1341,7 @@
         </is>
       </c>
       <c r="J10" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A10,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A10,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K10" s="15" t="inlineStr">
@@ -1393,7 +1396,7 @@
         </is>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A11,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A11,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K11" s="16" t="inlineStr">
@@ -1452,7 +1455,7 @@
         </is>
       </c>
       <c r="J12" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A12,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A12,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K12" s="15" t="inlineStr">
@@ -1507,7 +1510,7 @@
         </is>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A13,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A13,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K13" s="16" t="inlineStr">
@@ -1562,7 +1565,7 @@
         </is>
       </c>
       <c r="J14" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A14,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A14,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K14" s="15" t="inlineStr">
@@ -1617,7 +1620,7 @@
         </is>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A15,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A15,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K15" s="16" t="inlineStr">
@@ -1672,7 +1675,7 @@
         </is>
       </c>
       <c r="J16" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A16,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A16,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K16" s="15" t="inlineStr">
@@ -1731,7 +1734,7 @@
         </is>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A17,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A17,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K17" s="16" t="inlineStr">
@@ -1790,7 +1793,7 @@
         </is>
       </c>
       <c r="J18" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A18,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A18,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K18" s="15" t="inlineStr">
@@ -1845,7 +1848,7 @@
         </is>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A19,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A19,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K19" s="16" t="inlineStr">
@@ -1896,11 +1899,11 @@
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Kern</t>
         </is>
       </c>
       <c r="J20" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A20,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A20,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K20" s="15" t="inlineStr">
@@ -1913,7 +1916,11 @@
           <t>Erlaubt</t>
         </is>
       </c>
-      <c r="M20" s="15" t="n"/>
+      <c r="M20" s="15" t="inlineStr">
+        <is>
+          <t>Entscheidung DE/EN 14.10.2026</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="109.5" customHeight="1" s="11">
       <c r="A21" s="16" t="inlineStr">
@@ -1955,7 +1962,7 @@
         </is>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A21,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A21,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K21" s="16" t="inlineStr">
@@ -2014,7 +2021,7 @@
         </is>
       </c>
       <c r="J22" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A22,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A22,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K22" s="15" t="inlineStr">
@@ -2073,7 +2080,7 @@
         </is>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A23,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A23,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K23" s="16" t="inlineStr">
@@ -2128,7 +2135,7 @@
         </is>
       </c>
       <c r="J24" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A24,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A24,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K24" s="15" t="inlineStr">
@@ -2183,7 +2190,7 @@
         </is>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A25,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A25,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K25" s="16" t="inlineStr">
@@ -2238,7 +2245,7 @@
         </is>
       </c>
       <c r="J26" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A26,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A26,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K26" s="15" t="inlineStr">
@@ -2293,7 +2300,7 @@
         </is>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A27,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A27,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K27" s="16" t="inlineStr">
@@ -2348,7 +2355,7 @@
         </is>
       </c>
       <c r="J28" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A28,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A28,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K28" s="15" t="inlineStr">
@@ -2403,7 +2410,7 @@
         </is>
       </c>
       <c r="J29" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A29,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A29,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K29" s="16" t="inlineStr">
@@ -2458,7 +2465,7 @@
         </is>
       </c>
       <c r="J30" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A30,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A30,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K30" s="15" t="inlineStr">
@@ -2513,7 +2520,7 @@
         </is>
       </c>
       <c r="J31" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A31,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A31,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K31" s="16" t="inlineStr">
@@ -2568,7 +2575,7 @@
         </is>
       </c>
       <c r="J32" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A32,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A32,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K32" s="15" t="inlineStr">
@@ -2627,7 +2634,7 @@
         </is>
       </c>
       <c r="J33" s="16">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A33,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A33,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K33" s="16" t="inlineStr">
@@ -2686,7 +2693,7 @@
         </is>
       </c>
       <c r="J34" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A34,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A34,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K34" s="15" t="inlineStr">
@@ -2745,7 +2752,7 @@
         </is>
       </c>
       <c r="J35" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A35,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A35,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K35" s="15" t="inlineStr">
@@ -2804,7 +2811,7 @@
         </is>
       </c>
       <c r="J36" s="15">
-        <f>COUNTIFS(Tasks!$B$4:$B$139,A36,Tasks!$M$4:$M$139,"&lt;&gt;Gestrichen")</f>
+        <f>COUNTIFS(Tasks!$B$4:$B$1000,A36,Tasks!$M$4:$M$1000,"&lt;&gt;Gestrichen")</f>
         <v/>
       </c>
       <c r="K36" s="15" t="inlineStr">
@@ -2843,7 +2850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T139"/>
+  <dimension ref="A1:T141"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19" customWidth="1" style="10" min="1" max="1"/>
@@ -5393,7 +5400,7 @@
       </c>
       <c r="Q34" s="15" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Kern</t>
         </is>
       </c>
       <c r="R34" s="15" t="inlineStr">
@@ -5406,7 +5413,11 @@
           <t>Erlaubt</t>
         </is>
       </c>
-      <c r="T34" s="15" t="n"/>
+      <c r="T34" s="15" t="inlineStr">
+        <is>
+          <t>Entscheidung DE/EN 14.10.2026</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="67.5" customHeight="1" s="11">
       <c r="A35" s="16" t="inlineStr">
@@ -5470,7 +5481,7 @@
       </c>
       <c r="Q35" s="16" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Kern</t>
         </is>
       </c>
       <c r="R35" s="16" t="inlineStr">
@@ -5483,7 +5494,11 @@
           <t>Erlaubt</t>
         </is>
       </c>
-      <c r="T35" s="16" t="n"/>
+      <c r="T35" s="16" t="inlineStr">
+        <is>
+          <t>Entscheidung DE/EN 14.10.2026</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="67.5" customHeight="1" s="11">
       <c r="A36" s="15" t="inlineStr">
@@ -5547,7 +5562,7 @@
       </c>
       <c r="Q36" s="15" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Kern</t>
         </is>
       </c>
       <c r="R36" s="15" t="inlineStr">
@@ -5560,7 +5575,11 @@
           <t>Erlaubt</t>
         </is>
       </c>
-      <c r="T36" s="15" t="n"/>
+      <c r="T36" s="15" t="inlineStr">
+        <is>
+          <t>Entscheidung DE/EN 14.10.2026</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="67.5" customHeight="1" s="11">
       <c r="A37" s="16" t="inlineStr">
@@ -13794,6 +13813,160 @@
       <c r="T139" s="15" t="inlineStr">
         <is>
           <t>Neu nach D09 (EU-Datenschutz/AI Act).</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="15" customHeight="1" s="11">
+      <c r="A140" s="15" t="inlineStr">
+        <is>
+          <t>T-U017-04</t>
+        </is>
+      </c>
+      <c r="B140" s="15" t="inlineStr">
+        <is>
+          <t>U017</t>
+        </is>
+      </c>
+      <c r="C140" s="15" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D140" s="15" t="n"/>
+      <c r="E140" s="15" t="inlineStr">
+        <is>
+          <t>Englische Fassungen der Fachinhalte zur Prüfung vorbereiten</t>
+        </is>
+      </c>
+      <c r="F140" s="15" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="G140" s="19" t="n"/>
+      <c r="H140" s="19" t="n"/>
+      <c r="I140" s="18">
+        <f>(G140+H140)/2</f>
+        <v/>
+      </c>
+      <c r="J140" s="19" t="n"/>
+      <c r="K140" s="15" t="inlineStr">
+        <is>
+          <t>T-U009-01, T-U001-01</t>
+        </is>
+      </c>
+      <c r="L140" s="15" t="inlineStr">
+        <is>
+          <t>D07</t>
+        </is>
+      </c>
+      <c r="M140" s="19" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
+      </c>
+      <c r="N140" s="19" t="n"/>
+      <c r="O140" s="19" t="n"/>
+      <c r="P140" s="15" t="inlineStr">
+        <is>
+          <t>Unterstützend</t>
+        </is>
+      </c>
+      <c r="Q140" s="15" t="inlineStr">
+        <is>
+          <t>Kern</t>
+        </is>
+      </c>
+      <c r="R140" s="15" t="inlineStr">
+        <is>
+          <t>knowledge</t>
+        </is>
+      </c>
+      <c r="S140" s="15" t="inlineStr">
+        <is>
+          <t>Erlaubt</t>
+        </is>
+      </c>
+      <c r="T140" s="15" t="inlineStr">
+        <is>
+          <t>Neu nach Entscheidung DE/EN 14.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="15" customHeight="1" s="11">
+      <c r="A141" s="15" t="inlineStr">
+        <is>
+          <t>DOC-001</t>
+        </is>
+      </c>
+      <c r="B141" s="15" t="inlineStr">
+        <is>
+          <t>BASIS</t>
+        </is>
+      </c>
+      <c r="C141" s="15" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D141" s="15" t="n"/>
+      <c r="E141" s="15" t="inlineStr">
+        <is>
+          <t>Regelkonsistenz, knowledge-Format, Mehrsprachigkeit, Testlauf</t>
+        </is>
+      </c>
+      <c r="F141" s="15" t="inlineStr">
+        <is>
+          <t>Doku</t>
+        </is>
+      </c>
+      <c r="G141" s="19" t="n"/>
+      <c r="H141" s="19" t="n"/>
+      <c r="I141" s="18">
+        <f>(G141+H141)/2</f>
+        <v/>
+      </c>
+      <c r="J141" s="19" t="n"/>
+      <c r="K141" s="15" t="inlineStr">
+        <is>
+          <t>TEST-001, F002, F003</t>
+        </is>
+      </c>
+      <c r="L141" s="15" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="M141" s="19" t="inlineStr">
+        <is>
+          <t>Im Review</t>
+        </is>
+      </c>
+      <c r="N141" s="19" t="n"/>
+      <c r="O141" s="19" t="n"/>
+      <c r="P141" s="15" t="inlineStr">
+        <is>
+          <t>Nach menschlicher Freigabe</t>
+        </is>
+      </c>
+      <c r="Q141" s="15" t="inlineStr">
+        <is>
+          <t>Kern</t>
+        </is>
+      </c>
+      <c r="R141" s="15" t="inlineStr">
+        <is>
+          <t>docs, knowledge, contracts, scripts</t>
+        </is>
+      </c>
+      <c r="S141" s="15" t="inlineStr">
+        <is>
+          <t>Erlaubt</t>
+        </is>
+      </c>
+      <c r="T141" s="15" t="inlineStr">
+        <is>
+          <t>Neu nach TEST-001 und Entscheidungen 14.10.2026</t>
         </is>
       </c>
     </row>
@@ -13808,19 +13981,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="M4:M139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="M4:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
       <formula1>"Offen,Bereit,In Bearbeitung,Blockiert,Im Review,Erledigt,Gestrichen"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="O4:O139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="O4:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
       <formula1>"Mensch,Claude,Codex"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="G4:H139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" errorStyle="stop" operator="between">
+    <dataValidation sqref="G4:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" errorStyle="stop" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="J4:J139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="J4:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
       <formula1>"1,2,3,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -13840,7 +14013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19" customWidth="1" style="10" min="1" max="1"/>
@@ -18932,6 +19105,80 @@
       <c r="G139" s="15" t="inlineStr">
         <is>
           <t>U033</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="39.55" customHeight="1" s="11">
+      <c r="A140" s="15" t="inlineStr">
+        <is>
+          <t>T-U017-04</t>
+        </is>
+      </c>
+      <c r="B140" s="15" t="inlineStr">
+        <is>
+          <t>Bereite die englischen Fassungen der freigegebenen Fachinhalte zur fachlichen Prüfung vor. Gleiche id wie die deutsche Fassung, sprache en, Dateiname &lt;name&gt;.en.md.</t>
+        </is>
+      </c>
+      <c r="C140" s="15" t="inlineStr">
+        <is>
+          <t>Geprueft deutsche Fassung -&gt; englischer Entwurf zur Prüfung.</t>
+        </is>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>Je Inhalt existiert eine englische Datei mit gleicher id; Status hoechstens testfreigabe; kein Inhalt ohne deutsche Vorlage.</t>
+        </is>
+      </c>
+      <c r="E140" s="15" t="inlineStr">
+        <is>
+          <t>Fehlende englische Fassung führt zur deutschen Fassung mit Hinweis, nicht zu einer Übersetzung.</t>
+        </is>
+      </c>
+      <c r="F140" s="15" t="inlineStr">
+        <is>
+          <t>Nur den beschriebenen Teil umsetzen. Keine echten personenbezogenen Daten. Keine individuelle Bewertung, Diagnose oder Dringlichkeitseinstufung (D08). Keine maschinelle Übersetzung zur Laufzeit (harte Regel 12). Keine fachliche Freigabe setzen.</t>
+        </is>
+      </c>
+      <c r="G140" s="15" t="inlineStr">
+        <is>
+          <t>U017, D07</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="39.55" customHeight="1" s="11">
+      <c r="A141" s="15" t="inlineStr">
+        <is>
+          <t>DOC-001</t>
+        </is>
+      </c>
+      <c r="B141" s="15" t="inlineStr">
+        <is>
+          <t>Siehe planning/work-orders/DOC-001.md.</t>
+        </is>
+      </c>
+      <c r="C141" s="15" t="inlineStr">
+        <is>
+          <t>Befunde aus TEST-001 und Entscheidungen vom 14.10.2026 -&gt; angepasste Regeln und Doku.</t>
+        </is>
+      </c>
+      <c r="D141" s="15" t="inlineStr">
+        <is>
+          <t>Siehe Arbeitsauftrag.</t>
+        </is>
+      </c>
+      <c r="E141" s="15" t="inlineStr">
+        <is>
+          <t>Strukturcheck im Gut- und Fehlerfall; Vertragsbeispiele inklusive Gegenprobe.</t>
+        </is>
+      </c>
+      <c r="F141" s="15" t="inlineStr">
+        <is>
+          <t>Nur den beschriebenen Teil umsetzen. Keine echten personenbezogenen Daten. Keine individuelle Bewertung, Diagnose oder Dringlichkeitseinstufung (D08). Kein Produktcode.</t>
+        </is>
+      </c>
+      <c r="G141" s="15" t="inlineStr">
+        <is>
+          <t>TEST-001, F002, F003</t>
         </is>
       </c>
     </row>

--- a/planning/VitaSync_Coding_Backlog.xlsx
+++ b/planning/VitaSync_Coding_Backlog.xlsx
@@ -3041,8 +3041,16 @@
           <t>Erledigt</t>
         </is>
       </c>
-      <c r="N4" s="19" t="n"/>
-      <c r="O4" s="19" t="n"/>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>Atakan</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>Mensch</t>
+        </is>
+      </c>
       <c r="P4" s="15" t="inlineStr">
         <is>
           <t>Unterstützend</t>
@@ -3115,7 +3123,7 @@
       <c r="L5" s="16" t="n"/>
       <c r="M5" s="19" t="inlineStr">
         <is>
-          <t>Im Review</t>
+          <t>Erledigt</t>
         </is>
       </c>
       <c r="N5" s="19" t="inlineStr">
@@ -3148,7 +3156,11 @@
           <t>Erlaubt</t>
         </is>
       </c>
-      <c r="T5" s="16" t="n"/>
+      <c r="T5" s="16" t="inlineStr">
+        <is>
+          <t>PR #1 gemergt 14.10.2026</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="67.5" customHeight="1" s="11">
       <c r="A6" s="15" t="inlineStr">
@@ -3200,11 +3212,19 @@
       <c r="L6" s="15" t="n"/>
       <c r="M6" s="19" t="inlineStr">
         <is>
-          <t>Offen</t>
-        </is>
-      </c>
-      <c r="N6" s="19" t="n"/>
-      <c r="O6" s="19" t="n"/>
+          <t>Erledigt</t>
+        </is>
+      </c>
+      <c r="N6" s="19" t="inlineStr">
+        <is>
+          <t>Atakan</t>
+        </is>
+      </c>
+      <c r="O6" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
       <c r="P6" s="15" t="inlineStr">
         <is>
           <t>Unterstützend</t>
@@ -3225,7 +3245,11 @@
           <t>Erlaubt</t>
         </is>
       </c>
-      <c r="T6" s="15" t="n"/>
+      <c r="T6" s="15" t="inlineStr">
+        <is>
+          <t>PR #2 gemergt 14.10.2026</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="67.5" customHeight="1" s="11">
       <c r="A7" s="16" t="inlineStr">

--- a/planning/VitaSync_Coding_Backlog.xlsx
+++ b/planning/VitaSync_Coding_Backlog.xlsx
@@ -648,7 +648,7 @@
     <row r="5" ht="67.5" customHeight="1" s="11">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Offene Tasks</t>
+          <t>Nicht erledigt</t>
         </is>
       </c>
       <c r="B5" s="16" t="n"/>
@@ -13963,7 +13963,7 @@
       </c>
       <c r="M141" s="19" t="inlineStr">
         <is>
-          <t>Im Review</t>
+          <t>Erledigt</t>
         </is>
       </c>
       <c r="N141" s="19" t="n"/>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="T141" s="15" t="inlineStr">
         <is>
-          <t>Neu nach TEST-001 und Entscheidungen 14.10.2026</t>
+          <t>PR #3 gemergt 15.10.2026</t>
         </is>
       </c>
     </row>

--- a/planning/VitaSync_Coding_Backlog.xlsx
+++ b/planning/VitaSync_Coding_Backlog.xlsx
@@ -3301,11 +3301,19 @@
       <c r="L7" s="16" t="n"/>
       <c r="M7" s="19" t="inlineStr">
         <is>
-          <t>Offen</t>
-        </is>
-      </c>
-      <c r="N7" s="19" t="n"/>
-      <c r="O7" s="19" t="n"/>
+          <t>In Bearbeitung</t>
+        </is>
+      </c>
+      <c r="N7" s="19" t="inlineStr">
+        <is>
+          <t>Atakan</t>
+        </is>
+      </c>
+      <c r="O7" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
       <c r="P7" s="16" t="inlineStr">
         <is>
           <t>Nach menschlicher Freigabe</t>

--- a/planning/VitaSync_Coding_Backlog.xlsx
+++ b/planning/VitaSync_Coding_Backlog.xlsx
@@ -3301,7 +3301,7 @@
       <c r="L7" s="16" t="n"/>
       <c r="M7" s="19" t="inlineStr">
         <is>
-          <t>In Bearbeitung</t>
+          <t>Im Review</t>
         </is>
       </c>
       <c r="N7" s="19" t="inlineStr">
@@ -3334,7 +3334,11 @@
           <t>Erlaubt</t>
         </is>
       </c>
-      <c r="T7" s="16" t="n"/>
+      <c r="T7" s="16" t="inlineStr">
+        <is>
+          <t>PR #5, CI eingerichtet 15.10.2026</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="67.5" customHeight="1" s="11">
       <c r="A8" s="15" t="inlineStr">

--- a/planning/VitaSync_Coding_Backlog.xlsx
+++ b/planning/VitaSync_Coding_Backlog.xlsx
@@ -196,7 +196,7 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -244,6 +244,17 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFF4DAD4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -14011,9 +14022,14 @@
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="M4:M126">
+  <conditionalFormatting sqref="M4:M1000">
     <cfRule type="containsText" rank="0" priority="2" equalAverage="0" operator="containsText" aboveAverage="0" dxfId="5" text="Blockiert" percent="0" bottom="0">
       <formula>NOT(ISERROR(SEARCH("Blockiert",M4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:T1000">
+    <cfRule type="expression" priority="2" dxfId="6" stopIfTrue="0">
+      <formula>$M4="Erledigt"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">

--- a/planning/VitaSync_Coding_Backlog.xlsx
+++ b/planning/VitaSync_Coding_Backlog.xlsx
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TasksTable" displayName="TasksTable" ref="A3:T141" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TasksTable" displayName="TasksTable" ref="A3:T142" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:T141"/>
   <tableColumns count="20">
     <tableColumn id="1" name="Task-ID"/>
@@ -372,7 +372,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="BriefingsTable" displayName="BriefingsTable" ref="A3:G141" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="BriefingsTable" displayName="BriefingsTable" ref="A3:G142" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:G141"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Task-ID"/>
@@ -2850,7 +2850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T141"/>
+  <dimension ref="A1:T142"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19" customWidth="1" style="10" min="1" max="1"/>
@@ -13991,6 +13991,87 @@
       <c r="T141" s="15" t="inlineStr">
         <is>
           <t>PR #3 gemergt 15.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="15" customHeight="1" s="11">
+      <c r="A142" s="15" t="inlineStr">
+        <is>
+          <t>DOC-003</t>
+        </is>
+      </c>
+      <c r="B142" s="15" t="inlineStr">
+        <is>
+          <t>BASIS</t>
+        </is>
+      </c>
+      <c r="C142" s="15" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D142" s="15" t="n"/>
+      <c r="E142" s="15" t="inlineStr">
+        <is>
+          <t>Abgleich Research gegen Regelwerk als Notiz</t>
+        </is>
+      </c>
+      <c r="F142" s="15" t="inlineStr">
+        <is>
+          <t>Doku</t>
+        </is>
+      </c>
+      <c r="G142" s="19" t="n"/>
+      <c r="H142" s="19" t="n"/>
+      <c r="I142" s="18">
+        <f>(G142+H142)/2</f>
+        <v/>
+      </c>
+      <c r="J142" s="19" t="n"/>
+      <c r="K142" s="15" t="inlineStr">
+        <is>
+          <t>DOC-001</t>
+        </is>
+      </c>
+      <c r="L142" s="15" t="n"/>
+      <c r="M142" s="19" t="inlineStr">
+        <is>
+          <t>Im Review</t>
+        </is>
+      </c>
+      <c r="N142" s="19" t="inlineStr">
+        <is>
+          <t>Atakan</t>
+        </is>
+      </c>
+      <c r="O142" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="P142" s="15" t="inlineStr">
+        <is>
+          <t>Nach menschlicher Freigabe</t>
+        </is>
+      </c>
+      <c r="Q142" s="15" t="inlineStr">
+        <is>
+          <t>Kern</t>
+        </is>
+      </c>
+      <c r="R142" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="S142" s="15" t="inlineStr">
+        <is>
+          <t>Erlaubt</t>
+        </is>
+      </c>
+      <c r="T142" s="15" t="inlineStr">
+        <is>
+          <t>Notiz, keine Entscheidung; PR folgt</t>
         </is>
       </c>
     </row>
@@ -14037,7 +14118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19" customWidth="1" style="10" min="1" max="1"/>
@@ -19203,6 +19284,43 @@
       <c r="G141" s="15" t="inlineStr">
         <is>
           <t>TEST-001, F002, F003</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="39.55" customHeight="1" s="11">
+      <c r="A142" s="15" t="inlineStr">
+        <is>
+          <t>DOC-003</t>
+        </is>
+      </c>
+      <c r="B142" s="15" t="inlineStr">
+        <is>
+          <t>Siehe planning/work-orders/DOC-003.md.</t>
+        </is>
+      </c>
+      <c r="C142" s="15" t="inlineStr">
+        <is>
+          <t>research/ (10 Dateien) + Regelwerk -&gt; docs/Research-Abgleich.md.</t>
+        </is>
+      </c>
+      <c r="D142" s="15" t="inlineStr">
+        <is>
+          <t>Siehe Arbeitsauftrag.</t>
+        </is>
+      </c>
+      <c r="E142" s="15" t="inlineStr">
+        <is>
+          <t>Strukturcheck; Gegenlesen jeder Abweichung mit Quelle und Repo-Fundstelle.</t>
+        </is>
+      </c>
+      <c r="F142" s="15" t="inlineStr">
+        <is>
+          <t>Nur den beschriebenen Teil umsetzen. Keine Änderung an Entscheidungen, Regeln, contracts/ oder knowledge/. Keine neuen Backlog-Tasks. Keine individuelle Bewertung, Diagnose oder Dringlichkeitseinstufung (D08).</t>
+        </is>
+      </c>
+      <c r="G142" s="15" t="inlineStr">
+        <is>
+          <t>DOC-001</t>
         </is>
       </c>
     </row>

--- a/planning/VitaSync_Coding_Backlog.xlsx
+++ b/planning/VitaSync_Coding_Backlog.xlsx
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TasksTable" displayName="TasksTable" ref="A3:T141" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TasksTable" displayName="TasksTable" ref="A3:T142" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:T141"/>
   <tableColumns count="20">
     <tableColumn id="1" name="Task-ID"/>
@@ -372,7 +372,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="BriefingsTable" displayName="BriefingsTable" ref="A3:G141" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="BriefingsTable" displayName="BriefingsTable" ref="A3:G142" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A3:G141"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Task-ID"/>
@@ -2850,7 +2850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T141"/>
+  <dimension ref="A1:T1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19" customWidth="1" style="10" min="1" max="1"/>
@@ -13994,6 +13994,949 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="15" t="inlineStr">
+        <is>
+          <t>DOC-004</t>
+        </is>
+      </c>
+      <c r="B142" s="15" t="inlineStr">
+        <is>
+          <t>BASIS</t>
+        </is>
+      </c>
+      <c r="C142" s="15" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D142" s="15" t="n"/>
+      <c r="E142" s="15" t="inlineStr">
+        <is>
+          <t>Regeln: Quelldaten nur lesen, FHIR und OMOP, optionales Frontend PHP/JS</t>
+        </is>
+      </c>
+      <c r="F142" s="15" t="inlineStr">
+        <is>
+          <t>Doku</t>
+        </is>
+      </c>
+      <c r="G142" s="19" t="n"/>
+      <c r="H142" s="19" t="n"/>
+      <c r="I142" s="18">
+        <f>(G142+H142)/2</f>
+        <v/>
+      </c>
+      <c r="J142" s="19" t="n"/>
+      <c r="K142" s="15" t="inlineStr">
+        <is>
+          <t>DOC-001</t>
+        </is>
+      </c>
+      <c r="L142" s="15" t="inlineStr">
+        <is>
+          <t>D01, D02</t>
+        </is>
+      </c>
+      <c r="M142" s="19" t="inlineStr">
+        <is>
+          <t>Im Review</t>
+        </is>
+      </c>
+      <c r="N142" s="19" t="inlineStr">
+        <is>
+          <t>Atakan</t>
+        </is>
+      </c>
+      <c r="O142" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="P142" s="15" t="inlineStr">
+        <is>
+          <t>Nach menschlicher Freigabe</t>
+        </is>
+      </c>
+      <c r="Q142" s="15" t="inlineStr">
+        <is>
+          <t>Kern</t>
+        </is>
+      </c>
+      <c r="R142" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="S142" s="15" t="inlineStr">
+        <is>
+          <t>Erlaubt</t>
+        </is>
+      </c>
+      <c r="T142" s="15" t="inlineStr">
+        <is>
+          <t>Vorgaben Team 21.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
+    <row r="543"/>
+    <row r="544"/>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547"/>
+    <row r="548"/>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937"/>
+    <row r="938"/>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952"/>
+    <row r="953"/>
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
+    <row r="965"/>
+    <row r="966"/>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
+    <row r="993"/>
+    <row r="994"/>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:Q2"/>
@@ -14037,7 +14980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19" customWidth="1" style="10" min="1" max="1"/>
@@ -19203,6 +20146,43 @@
       <c r="G141" s="15" t="inlineStr">
         <is>
           <t>TEST-001, F002, F003</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="15" t="inlineStr">
+        <is>
+          <t>DOC-004</t>
+        </is>
+      </c>
+      <c r="B142" s="15" t="inlineStr">
+        <is>
+          <t>Siehe planning/work-orders/DOC-004.md.</t>
+        </is>
+      </c>
+      <c r="C142" s="15" t="inlineStr">
+        <is>
+          <t>Teamvorgaben -&gt; harte Regel 14, D01, D02, Architektur.</t>
+        </is>
+      </c>
+      <c r="D142" s="15" t="inlineStr">
+        <is>
+          <t>Siehe Arbeitsauftrag.</t>
+        </is>
+      </c>
+      <c r="E142" s="15" t="inlineStr">
+        <is>
+          <t>Strukturcheck.</t>
+        </is>
+      </c>
+      <c r="F142" s="15" t="inlineStr">
+        <is>
+          <t>Nur den beschriebenen Teil umsetzen. Kein Produktcode. Keine Änderung an D08. Keine individuelle Bewertung, Diagnose oder Dringlichkeitseinstufung (D08).</t>
+        </is>
+      </c>
+      <c r="G142" s="15" t="inlineStr">
+        <is>
+          <t>DOC-001</t>
         </is>
       </c>
     </row>
